--- a/data/trans_orig/IP16A05-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP16A05-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>520</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4800</t>
+          <t>4633</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1339</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7290</t>
+          <t>7635</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2556</t>
+          <t>2390</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9728</t>
+          <t>9478</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,15%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24235</t>
+          <t>24402</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28522</t>
+          <t>28515</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>84,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22365</t>
+          <t>22020</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28316</t>
+          <t>28356</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,42%</t>
+          <t>74,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>48962</t>
+          <t>49212</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>56134</t>
+          <t>56300</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,93%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3284</t>
+          <t>2813</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10771</t>
+          <t>10531</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3826</t>
+          <t>3765</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11522</t>
+          <t>11775</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8526</t>
+          <t>8520</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19489</t>
+          <t>19278</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,47%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>32450</t>
+          <t>32690</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>39937</t>
+          <t>40408</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,08%</t>
+          <t>75,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>39438</t>
+          <t>39185</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>47134</t>
+          <t>47195</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>76,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>74692</t>
+          <t>74903</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>85655</t>
+          <t>85661</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>79,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4545</t>
+          <t>3931</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>694</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6132</t>
+          <t>6264</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1894</t>
+          <t>1413</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8200</t>
+          <t>7794</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>16,81%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17962</t>
+          <t>18576</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17734</t>
+          <t>17602</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23191</t>
+          <t>23172</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,31%</t>
+          <t>73,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>38173</t>
+          <t>38579</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>44479</t>
+          <t>44960</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>83,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>96,95%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>612</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5370</t>
+          <t>5146</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4317</t>
+          <t>4275</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>1249</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7271</t>
+          <t>7185</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,27%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>25173</t>
+          <t>25397</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>29953</t>
+          <t>29931</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>83,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>35121</t>
+          <t>35163</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>62710</t>
+          <t>62796</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>68719</t>
+          <t>68732</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,22%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6445</t>
+          <t>6600</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17141</t>
+          <t>17356</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>9481</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21384</t>
+          <t>20949</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18490</t>
+          <t>17591</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>34483</t>
+          <t>34355</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,76%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>108164</t>
+          <t>107949</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>118860</t>
+          <t>118705</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>122535</t>
+          <t>122970</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>134127</t>
+          <t>134438</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>234741</t>
+          <t>234869</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>250734</t>
+          <t>251633</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,47%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3359</t>
+          <t>3642</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10866</t>
+          <t>11178</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2237</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9585</t>
+          <t>8999</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7040</t>
+          <t>6721</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17312</t>
+          <t>16673</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>22,25%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25631</t>
+          <t>25319</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33138</t>
+          <t>32855</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,23%</t>
+          <t>69,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28841</t>
+          <t>29427</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>36189</t>
+          <t>36446</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>76,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>57611</t>
+          <t>58250</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>67883</t>
+          <t>68202</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,89%</t>
+          <t>77,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>91,03%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5891</t>
+          <t>6349</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16192</t>
+          <t>16489</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6460</t>
+          <t>6392</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16853</t>
+          <t>17100</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15020</t>
+          <t>15019</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29684</t>
+          <t>29636</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,51%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>37973</t>
+          <t>37676</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>48274</t>
+          <t>47816</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,11%</t>
+          <t>69,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>49904</t>
+          <t>49657</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>60297</t>
+          <t>60365</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,75%</t>
+          <t>74,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>91238</t>
+          <t>91286</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>105902</t>
+          <t>105903</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,45%</t>
+          <t>75,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2130</t>
+          <t>2266</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8973</t>
+          <t>9738</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1115</t>
+          <t>858</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8064</t>
+          <t>7143</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4562</t>
+          <t>4515</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14069</t>
+          <t>13942</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,13%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20897</t>
+          <t>20132</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27740</t>
+          <t>27604</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,96%</t>
+          <t>67,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19851</t>
+          <t>20772</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26800</t>
+          <t>27057</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,11%</t>
+          <t>74,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>43716</t>
+          <t>43843</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>53223</t>
+          <t>53270</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>75,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,19%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1593</t>
+          <t>1971</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8348</t>
+          <t>8245</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3876</t>
+          <t>4516</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2627</t>
+          <t>2731</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10066</t>
+          <t>10116</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,44%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>18821</t>
+          <t>18924</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>25576</t>
+          <t>25198</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,27%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,7 +3857,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>20992</t>
+          <t>20352</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,41%</t>
+          <t>81,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>41971</t>
+          <t>41921</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>49410</t>
+          <t>49306</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>80,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,75%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18949</t>
+          <t>19150</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>34234</t>
+          <t>34373</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13999</t>
+          <t>14362</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28216</t>
+          <t>29524</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>37430</t>
+          <t>36772</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>58313</t>
+          <t>58807</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,24%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>113467</t>
+          <t>113328</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>128752</t>
+          <t>128551</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>76,82%</t>
+          <t>76,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>129750</t>
+          <t>128442</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>143967</t>
+          <t>143604</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>81,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>247354</t>
+          <t>246860</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>268237</t>
+          <t>268895</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>87,97%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2507</t>
+          <t>2731</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8998</t>
+          <t>9599</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>35,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1963</t>
+          <t>2066</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8930</t>
+          <t>8618</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6045</t>
+          <t>6214</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14940</t>
+          <t>15128</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,66%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18035</t>
+          <t>17434</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24526</t>
+          <t>24302</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,71%</t>
+          <t>64,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15046</t>
+          <t>15358</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22013</t>
+          <t>21910</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,76%</t>
+          <t>64,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>36069</t>
+          <t>35881</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>44964</t>
+          <t>44795</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,71%</t>
+          <t>70,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>87,82%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3059</t>
+          <t>3082</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10629</t>
+          <t>10527</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2443</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9425</t>
+          <t>10413</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7259</t>
+          <t>7338</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17171</t>
+          <t>17779</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,83%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>31610</t>
+          <t>31712</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>39180</t>
+          <t>39157</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,84%</t>
+          <t>75,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>33671</t>
+          <t>32683</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>40653</t>
+          <t>40451</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,13%</t>
+          <t>75,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>68164</t>
+          <t>67556</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>78076</t>
+          <t>77997</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>79,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,4%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>545</t>
+          <t>551</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4812</t>
+          <t>4779</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2147</t>
+          <t>1715</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9695</t>
+          <t>8995</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3137</t>
+          <t>3202</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11243</t>
+          <t>10964</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>15,76%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31312</t>
+          <t>31345</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>35579</t>
+          <t>35573</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>86,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23751</t>
+          <t>24451</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>31299</t>
+          <t>31731</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,01%</t>
+          <t>73,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>58327</t>
+          <t>58606</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>66433</t>
+          <t>66368</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>84,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,4%</t>
         </is>
       </c>
     </row>
@@ -5661,7 +5661,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4747</t>
+          <t>4778</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5696,7 +5696,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4702</t>
+          <t>5120</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>774</t>
+          <t>765</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7547</t>
+          <t>7066</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>15,76%</t>
         </is>
       </c>
     </row>
@@ -5769,7 +5769,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>17318</t>
+          <t>17287</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,49%</t>
+          <t>78,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5804,7 +5804,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>18056</t>
+          <t>17638</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>77,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>37276</t>
+          <t>37757</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>44049</t>
+          <t>44058</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,16%</t>
+          <t>84,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,29%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9846</t>
+          <t>9561</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21561</t>
+          <t>20678</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10193</t>
+          <t>10447</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23328</t>
+          <t>23916</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>23748</t>
+          <t>22883</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>40852</t>
+          <t>40249</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,05%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>105900</t>
+          <t>106783</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>117615</t>
+          <t>117900</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>99948</t>
+          <t>99360</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>113083</t>
+          <t>112829</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>80,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>209885</t>
+          <t>210488</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>226989</t>
+          <t>227854</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,71%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,87%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1255</t>
+          <t>1311</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6455</t>
+          <t>6280</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>39,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6614,7 +6614,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2123</t>
+          <t>2701</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6629,7 +6629,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1550</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7438</t>
+          <t>7917</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>20,65%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9528</t>
+          <t>9703</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14728</t>
+          <t>14672</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,61%</t>
+          <t>60,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20234</t>
+          <t>19656</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>87,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>30902</t>
+          <t>30423</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36790</t>
+          <t>36827</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>79,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,05%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3365</t>
+          <t>3165</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16405</t>
+          <t>15924</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2706</t>
+          <t>2695</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10194</t>
+          <t>10728</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7490</t>
+          <t>8038</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22623</t>
+          <t>22509</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,54%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>30218</t>
+          <t>30699</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>43258</t>
+          <t>43458</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>64,81%</t>
+          <t>65,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>38790</t>
+          <t>38256</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>46278</t>
+          <t>46289</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>78,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>72984</t>
+          <t>73098</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>88117</t>
+          <t>87569</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,34%</t>
+          <t>76,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>91,59%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1159</t>
+          <t>1127</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6942</t>
+          <t>7040</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>880</t>
+          <t>841</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8397</t>
+          <t>8152</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2830</t>
+          <t>2813</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11999</t>
+          <t>11746</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,1%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>30209</t>
+          <t>30111</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>35992</t>
+          <t>36024</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,31%</t>
+          <t>81,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>37772</t>
+          <t>38017</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>45289</t>
+          <t>45328</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>71321</t>
+          <t>71574</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>80490</t>
+          <t>80507</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,62%</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4660</t>
+          <t>4796</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7623,7 +7623,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7643,7 +7643,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3169</t>
+          <t>3572</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>457</t>
+          <t>510</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>5578</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -7716,7 +7716,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>73297</t>
+          <t>73161</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -7731,7 +7731,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7751,7 +7751,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>61523</t>
+          <t>61120</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>137429</t>
+          <t>137071</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>142192</t>
+          <t>142139</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,64%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8044</t>
+          <t>7984</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25937</t>
+          <t>25286</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5777</t>
+          <t>5454</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17076</t>
+          <t>16563</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16992</t>
+          <t>16231</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>35777</t>
+          <t>36075</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,02%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>151778</t>
+          <t>152429</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>169671</t>
+          <t>169731</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>165125</t>
+          <t>165638</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>176424</t>
+          <t>176747</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>324139</t>
+          <t>323841</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>342924</t>
+          <t>343685</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,49%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP16A05-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP16A05-Edad-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3532</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1313</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7765</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>11,91%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>4,43%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>26,18%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>1756</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>520</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4633</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>508</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4663</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>6,05%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,79%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>15,96%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>3532</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1299</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>7635</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>11,91%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2390</t>
+          <t>2584</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9478</t>
+          <t>9607</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,37%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>26123</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>21890</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>28342</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>88,09%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>73,82%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>95,57%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>27279</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>24402</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>28515</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>24372</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>28527</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>93,95%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>84,04%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>98,21%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>26123</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>22020</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>28356</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>88,09%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>49212</t>
+          <t>49083</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>56300</t>
+          <t>56106</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>83,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,6%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>29655</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>29655</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>29655</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>29035</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>29035</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>29035</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>29655</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>29655</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>29655</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>7127</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3800</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>11579</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>13,99%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>7,46%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>22,72%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>6118</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2813</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>10531</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>3220</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>10496</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>14,16%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>6,51%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>24,36%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>7127</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>3765</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>11775</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>13,99%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8520</t>
+          <t>8321</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19278</t>
+          <t>19853</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>21,08%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>43833</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>39381</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>47160</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>86,01%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>77,28%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>92,54%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>37103</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>32690</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>40408</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>32725</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>40001</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>85,84%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>75,64%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>93,49%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>43833</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>39185</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>47195</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>86,01%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,89%</t>
+          <t>75,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>74903</t>
+          <t>74328</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>85661</t>
+          <t>85860</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>78,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>91,16%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>50960</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>50960</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>50960</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>43221</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>43221</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>43221</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>50960</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>50960</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>50960</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2751</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5654</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>11,53%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2,88%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>23,69%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>1296</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3931</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3973</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>5,76%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>17,47%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>2751</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>694</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>6264</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>11,53%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>2,91%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1413</t>
+          <t>1424</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7794</t>
+          <t>8677</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>18,71%</t>
         </is>
       </c>
     </row>
@@ -1522,74 +1522,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>21115</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>18212</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>23179</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>88,47%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>76,31%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>97,12%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>21211</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>18576</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>18534</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>22507</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>94,24%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>82,53%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>82,35%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>21115</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>17602</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>23172</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>88,47%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>73,75%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>97,09%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>63</t>
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>38579</t>
+          <t>37696</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>44960</t>
+          <t>44949</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,19%</t>
+          <t>81,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,93%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>23866</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>23866</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>23866</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>22507</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>22507</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>22507</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>23866</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>23866</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>23866</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1272</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4527</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3,23%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>11,48%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1985</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5146</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>608</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5875</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>6,5%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>16,85%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1272</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4275</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>3,23%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1249</t>
+          <t>1231</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7185</t>
+          <t>7419</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,6%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>38166</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>34911</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>39438</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>96,77%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>88,52%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>28558</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>25397</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>29931</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>24668</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>29935</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>93,5%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>83,15%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>98,0%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>38166</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>35163</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>39438</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>96,77%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>80,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>62796</t>
+          <t>62562</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>68732</t>
+          <t>68750</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,24%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>39438</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>39438</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>39438</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>30543</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>30543</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>30543</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>39438</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>39438</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>39438</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>14682</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>9344</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>21724</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>10,2%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>6,49%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>15,09%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>11155</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>6600</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>17356</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>6900</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>17203</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>8,9%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>5,27%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>13,85%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>14682</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>9481</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>20949</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>10,2%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17591</t>
+          <t>18380</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>34355</t>
+          <t>33703</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,52%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>129237</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>122195</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>134575</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>89,8%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>84,91%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>93,51%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>173</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>114150</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>107949</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>118705</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>108102</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>118405</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>91,1%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>86,15%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>94,73%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>193</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>129237</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>122970</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>134438</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>89,8%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>234869</t>
+          <t>235521</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>251633</t>
+          <t>250844</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>87,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,17%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>125305</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4865</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1945</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>9320</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>12,66%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>5,06%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>24,25%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>6520</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3642</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>11178</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>3290</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>10785</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>17,86%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>9,98%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>30,63%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>4865</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1980</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>8999</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>12,66%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6721</t>
+          <t>6914</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16673</t>
+          <t>17240</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>23,01%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>33561</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>29106</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>36481</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>87,34%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>75,75%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>94,94%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>29977</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>25319</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>32855</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>25712</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>33207</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>82,14%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>69,37%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>90,02%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>33561</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>29427</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>36446</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>87,34%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>70,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>58250</t>
+          <t>57683</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>68202</t>
+          <t>68009</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,75%</t>
+          <t>76,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>90,77%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>38426</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>38426</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>38426</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>36497</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>36497</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>36497</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>38426</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>38426</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>38426</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>11055</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>6422</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>16724</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>16,56%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>9,62%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>25,05%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>10538</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>6349</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>16489</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>6192</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>16578</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>19,46%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>11,72%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>30,44%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>11055</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>6392</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>17100</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>16,56%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15019</t>
+          <t>14959</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29636</t>
+          <t>29695</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,56%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>55702</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>50033</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>60335</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>83,44%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>74,95%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>90,38%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>43627</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>37676</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>47816</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>37587</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>47973</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>80,54%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>69,56%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>88,28%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>55702</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>49657</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>60365</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>83,44%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,38%</t>
+          <t>69,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>88,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>91286</t>
+          <t>91227</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>105903</t>
+          <t>105963</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,49%</t>
+          <t>75,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>87,63%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>66757</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>66757</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>66757</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>54165</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>54165</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>54165</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>66757</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>66757</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>66757</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3269</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>848</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7552</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>11,71%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3,04%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>27,06%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>5039</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2266</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>9738</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2084</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>8929</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>16,87%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>7,59%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>32,6%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>3269</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>858</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>7143</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>11,71%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4515</t>
+          <t>4489</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13942</t>
+          <t>13857</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>23,98%</t>
         </is>
       </c>
     </row>
@@ -3474,67 +3474,67 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>24646</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>20363</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>27067</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>88,29%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>72,94%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>96,96%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
           <t>24831</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>20132</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>27604</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>20941</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>27786</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>83,13%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>67,4%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>92,41%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>24646</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>20772</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>27057</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>88,29%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,41%</t>
+          <t>70,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>43843</t>
+          <t>43928</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>53270</t>
+          <t>53296</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>76,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,23%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>27915</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>27915</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>27915</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>29870</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>29870</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>29870</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>27915</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>27915</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>27915</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1275</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3989</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>5,13%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>16,04%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>4278</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1971</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>8245</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1989</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>8297</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>15,75%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>7,25%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>30,35%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1275</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4516</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>5,13%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>30,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2731</t>
+          <t>2643</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10116</t>
+          <t>10262</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,72%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>23593</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>20879</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>24868</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>94,87%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>83,96%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>22891</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>18924</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>25198</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>18872</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>25180</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>84,25%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>69,65%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>92,75%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>23593</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>20352</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>24868</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>94,87%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>69,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>41921</t>
+          <t>41775</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>49306</t>
+          <t>49394</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>80,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,92%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>24868</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>24868</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>24868</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>27169</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>27169</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>27169</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>24868</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>24868</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>24868</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>20465</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>13930</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>28618</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>12,96%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>8,82%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>18,12%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>26375</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>19150</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>34373</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>19018</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>35328</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>17,86%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>12,97%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>23,27%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>20465</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>14362</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>29524</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>12,96%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>36772</t>
+          <t>37446</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>58807</t>
+          <t>58597</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,17%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>137501</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>129348</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>144036</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>87,04%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>81,88%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>91,18%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>176</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>121326</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>113328</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>128551</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>112373</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>128683</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>82,14%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>76,73%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>87,03%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>137501</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>128442</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>143604</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>87,04%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,31%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>246860</t>
+          <t>247070</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>268895</t>
+          <t>268221</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>80,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>87,75%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>157966</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>157966</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>157966</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>213</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>147701</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>147701</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>147701</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>157966</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>157966</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>157966</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4616</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8270</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>19,25%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>8,42%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>34,49%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>5359</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2731</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>9599</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2706</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>19,82%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>10,1%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>35,51%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>4616</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2066</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>8618</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>19,25%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6214</t>
+          <t>6171</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15128</t>
+          <t>15299</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>29,99%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>19360</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>15706</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>21956</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>80,75%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>65,51%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>91,58%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>21674</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>17434</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>24302</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>17914</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>24327</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>80,18%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>64,49%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>89,9%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>19360</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>15358</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>21910</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>80,75%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>64,06%</t>
+          <t>66,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>35881</t>
+          <t>35710</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>44795</t>
+          <t>44838</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,34%</t>
+          <t>70,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,9%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>23976</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>23976</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>23976</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>27033</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>27033</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>27033</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>23976</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>23976</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>23976</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>5367</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2597</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>10527</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>12,45%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>6,03%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>24,43%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>6217</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>3082</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>10527</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>3575</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>11375</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>14,72%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>7,3%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>24,92%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>5367</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>2645</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>10413</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>12,45%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7338</t>
+          <t>6890</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17779</t>
+          <t>16670</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>19,53%</t>
         </is>
       </c>
     </row>
@@ -5078,67 +5078,67 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>37729</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>32569</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>40499</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>87,55%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>75,57%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>93,97%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
           <t>36022</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>31712</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>39157</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>30864</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>38664</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>85,28%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>75,08%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>92,7%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>37729</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>32683</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>40451</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>87,55%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>73,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>67556</t>
+          <t>68665</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>77997</t>
+          <t>78445</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,17%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,93%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>43096</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>43096</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>43096</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>42239</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>42239</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>42239</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>43096</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>43096</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>43096</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4561</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2118</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>8827</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>13,64%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>6,33%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>26,39%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>1745</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>551</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4779</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4769</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>4,83%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,53%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>13,23%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>4561</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1715</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>8995</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>13,64%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3202</t>
+          <t>2979</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10964</t>
+          <t>11058</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,89%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>28885</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>24619</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>31328</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>86,36%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>73,61%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>93,67%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>34379</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>31345</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>35573</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>31355</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>35574</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>95,17%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>86,77%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>98,47%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>28885</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>24451</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>31731</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>86,36%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,11%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>58606</t>
+          <t>58512</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>66368</t>
+          <t>66591</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,72%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>33446</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>33446</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>33446</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>36124</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>36124</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>36124</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>33446</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>33446</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>33446</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5651,67 +5651,67 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>1514</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4601</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>6,65%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>20,22%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>1574</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4778</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4905</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>7,13%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>21,65%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1514</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5120</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>6,65%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>765</t>
+          <t>822</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7066</t>
+          <t>7548</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>16,84%</t>
         </is>
       </c>
     </row>
@@ -5764,69 +5764,69 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>21244</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>18157</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>22758</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>93,35%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>79,78%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
           <t>20491</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>17287</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>17160</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>22065</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>92,87%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>78,35%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>77,77%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>21244</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>17638</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>22758</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>93,35%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>77,5%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>58</t>
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>37757</t>
+          <t>37275</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>44058</t>
+          <t>44001</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>83,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,17%</t>
         </is>
       </c>
     </row>
@@ -5877,52 +5877,52 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>22758</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>22758</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>22758</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
           <t>22065</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>22065</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>22065</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>22758</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>22758</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>22758</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5994,67 +5994,67 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>16058</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>10764</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>23141</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>13,03%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>8,73%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>18,77%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
           <t>14895</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>9561</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>20678</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>9591</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>21149</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>11,69%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>7,5%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>16,22%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>16058</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>10447</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>23916</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>13,03%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>22883</t>
+          <t>23666</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>40249</t>
+          <t>40267</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,06%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>107218</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>100135</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>112512</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>86,97%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>81,23%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>91,27%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>168</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>112566</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>106783</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>117900</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>106312</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>117870</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>88,31%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>83,78%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>92,5%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>107218</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>99360</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>112829</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>86,97%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>83,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>210488</t>
+          <t>210470</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>227854</t>
+          <t>227071</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,56%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>192</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>127461</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>127461</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>127461</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>123276</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>123276</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>123276</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2270</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1,95%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>13,02%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>3328</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1311</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6280</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>20,82%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>8,2%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>39,29%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>425</t>
+          <t>3133</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1183</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2701</t>
+          <t>5955</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>42,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>3754</t>
+          <t>3473</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>1360</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7917</t>
+          <t>6887</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>21,79%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>17093</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>15163</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>17433</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>98,05%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>86,98%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>12655</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>9703</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>14672</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>79,18%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>60,71%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>91,8%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>21932</t>
+          <t>11036</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19656</t>
+          <t>8214</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22357</t>
+          <t>12986</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>77,89%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>57,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>34586</t>
+          <t>28128</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>30423</t>
+          <t>24714</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36827</t>
+          <t>30241</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>78,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>95,7%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>17433</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>17433</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>17433</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>15983</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>15983</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>15983</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>22357</t>
+          <t>14169</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>22357</t>
+          <t>14169</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22357</t>
+          <t>14169</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>38340</t>
+          <t>31601</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>38340</t>
+          <t>31601</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>38340</t>
+          <t>31601</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4978</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2334</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>9293</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>12,07%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>5,66%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>22,54%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>7263</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>3165</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>15924</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>15,58%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>6,79%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>34,16%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5749</t>
+          <t>4170</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2695</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10728</t>
+          <t>7504</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>13012</t>
+          <t>9148</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8038</t>
+          <t>5607</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22509</t>
+          <t>14677</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>17,87%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>36257</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>31942</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>38901</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>87,93%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>77,46%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>94,34%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>39360</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>30699</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>43458</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>84,42%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>65,84%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>93,21%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>43235</t>
+          <t>36726</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>38256</t>
+          <t>33392</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>46289</t>
+          <t>38898</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,1%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>82595</t>
+          <t>72983</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>73098</t>
+          <t>67454</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>87569</t>
+          <t>76524</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>82,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>93,17%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>41235</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>41235</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>41235</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>46623</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>46623</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>46623</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>48984</t>
+          <t>40896</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>48984</t>
+          <t>40896</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>48984</t>
+          <t>40896</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>95607</t>
+          <t>82131</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>95607</t>
+          <t>82131</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>95607</t>
+          <t>82131</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3009</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>866</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7762</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>6,84%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,97%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>17,65%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>3152</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1127</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7040</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>8,48%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,03%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>18,95%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3004</t>
+          <t>3271</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>841</t>
+          <t>1193</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8152</t>
+          <t>7133</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>6156</t>
+          <t>6280</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2813</t>
+          <t>2637</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11746</t>
+          <t>11648</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,22%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>40962</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>36209</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>43105</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>93,16%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>82,35%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>98,03%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>33999</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>30111</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>36024</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>91,52%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>81,05%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>96,97%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>43165</t>
+          <t>34677</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>38017</t>
+          <t>30815</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>45328</t>
+          <t>36755</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>81,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>77164</t>
+          <t>75639</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>71574</t>
+          <t>70271</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>80507</t>
+          <t>79282</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>85,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,78%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>43971</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>43971</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>43971</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>37151</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>37151</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>37151</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>46169</t>
+          <t>37948</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>46169</t>
+          <t>37948</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>46169</t>
+          <t>37948</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>83320</t>
+          <t>81919</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>83320</t>
+          <t>81919</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>83320</t>
+          <t>81919</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>608</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3760</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>6,03%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>1269</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1337</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4796</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4652</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>2,67%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>6,15%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>621</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3572</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1890</t>
+          <t>1945</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>510</t>
+          <t>529</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5578</t>
+          <t>5344</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
@@ -7706,74 +7706,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>61705</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>58553</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>62313</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,02%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>93,97%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>76688</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>73161</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>77957</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>98,37%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>93,85%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>48643</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>45328</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>49980</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>97,33%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>90,69%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>64071</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>61120</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>64692</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,04%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>94,48%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>145</t>
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>140759</t>
+          <t>110348</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>137071</t>
+          <t>106949</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>142139</t>
+          <t>111764</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,53%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>62313</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>62313</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>62313</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>77957</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>77957</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>77957</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>64692</t>
+          <t>49980</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>64692</t>
+          <t>49980</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>64692</t>
+          <t>49980</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>142649</t>
+          <t>112293</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>142649</t>
+          <t>112293</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>142649</t>
+          <t>112293</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>8935</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>4658</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>15696</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>5,42%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2,82%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>9,52%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>15013</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>7984</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>25286</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>8,45%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>4,49%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>14,23%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>9798</t>
+          <t>11912</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5454</t>
+          <t>7662</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16563</t>
+          <t>18239</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>24812</t>
+          <t>20846</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16231</t>
+          <t>14164</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>36075</t>
+          <t>28753</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,34%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>156017</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>149256</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>160294</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>94,58%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>90,48%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>97,18%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>205</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>162702</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>152429</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>169731</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>91,55%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>85,77%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>95,51%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>172403</t>
+          <t>131080</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>165638</t>
+          <t>124753</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>176747</t>
+          <t>135330</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>335104</t>
+          <t>287098</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>323841</t>
+          <t>279191</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>343685</t>
+          <t>293780</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,4%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
